--- a/checklist/1783606423.xlsx
+++ b/checklist/1783606423.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{AF79E293-9A8B-438A-B307-67EF33A802E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25FB5FFE-D2EE-47E7-9B4F-BC8707E57F46}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{AF79E293-9A8B-438A-B307-67EF33A802E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F800E05A-2CB2-4198-BD36-A6E503EAE713}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -936,6 +936,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1168,7 +1172,7 @@
       <c r="C4" s="16"/>
       <c r="D4" s="17" t="str">
         <f>COUNTIF(F7:F59,"Done")&amp;" of "&amp;COUNTA(F7:F59)&amp;" done   ("&amp;TEXT(COUNTIF(F7:F59,"Done")/COUNTA(F7:F59),"0%")&amp;" complete)   |   In Progress: "&amp;COUNTIF(F7:F59,"In Progress")&amp;"   |   Blocked: "&amp;COUNTIF(F7:F59,"Blocked")</f>
-        <v>4 of 53 done   (8% complete)   |   In Progress: 0   |   Blocked: 0</v>
+        <v>8 of 53 done   (15% complete)   |   In Progress: 0   |   Blocked: 0</v>
       </c>
       <c r="E4" s="17"/>
       <c r="F4" s="17"/>
@@ -1330,7 +1334,7 @@
         <v>24</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>12</v>
+        <v>161</v>
       </c>
       <c r="G13" s="5"/>
     </row>
@@ -1349,7 +1353,7 @@
         <v>24</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>12</v>
+        <v>161</v>
       </c>
       <c r="G14" s="10"/>
     </row>
@@ -1368,7 +1372,7 @@
         <v>29</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>12</v>
+        <v>161</v>
       </c>
       <c r="G15" s="5"/>
     </row>
@@ -1387,7 +1391,7 @@
         <v>29</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>12</v>
+        <v>161</v>
       </c>
       <c r="G16" s="10"/>
     </row>

--- a/checklist/1783606423.xlsx
+++ b/checklist/1783606423.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{AF79E293-9A8B-438A-B307-67EF33A802E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F800E05A-2CB2-4198-BD36-A6E503EAE713}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="13_ncr:1_{AF79E293-9A8B-438A-B307-67EF33A802E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F9F7A33E-2E57-4B00-BEB9-3E6B98CE199D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1172,7 +1172,7 @@
       <c r="C4" s="16"/>
       <c r="D4" s="17" t="str">
         <f>COUNTIF(F7:F59,"Done")&amp;" of "&amp;COUNTA(F7:F59)&amp;" done   ("&amp;TEXT(COUNTIF(F7:F59,"Done")/COUNTA(F7:F59),"0%")&amp;" complete)   |   In Progress: "&amp;COUNTIF(F7:F59,"In Progress")&amp;"   |   Blocked: "&amp;COUNTIF(F7:F59,"Blocked")</f>
-        <v>8 of 53 done   (15% complete)   |   In Progress: 0   |   Blocked: 0</v>
+        <v>24 of 53 done   (45% complete)   |   In Progress: 0   |   Blocked: 0</v>
       </c>
       <c r="E4" s="17"/>
       <c r="F4" s="17"/>
@@ -1294,7 +1294,7 @@
         <v>11</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>12</v>
+        <v>161</v>
       </c>
       <c r="G11" s="5"/>
     </row>
@@ -1313,7 +1313,7 @@
         <v>11</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>12</v>
+        <v>161</v>
       </c>
       <c r="G12" s="10"/>
     </row>
@@ -1410,7 +1410,7 @@
         <v>34</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>12</v>
+        <v>161</v>
       </c>
       <c r="G17" s="5"/>
     </row>
@@ -1429,7 +1429,7 @@
         <v>34</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>12</v>
+        <v>161</v>
       </c>
       <c r="G18" s="10"/>
     </row>
@@ -1448,7 +1448,7 @@
         <v>34</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>12</v>
+        <v>161</v>
       </c>
       <c r="G19" s="5"/>
     </row>
@@ -1467,7 +1467,7 @@
         <v>41</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>12</v>
+        <v>161</v>
       </c>
       <c r="G20" s="10"/>
     </row>
@@ -1486,7 +1486,7 @@
         <v>41</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>12</v>
+        <v>161</v>
       </c>
       <c r="G21" s="5"/>
     </row>
@@ -1505,7 +1505,7 @@
         <v>41</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>12</v>
+        <v>161</v>
       </c>
       <c r="G22" s="10"/>
     </row>
@@ -1524,7 +1524,7 @@
         <v>48</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>12</v>
+        <v>161</v>
       </c>
       <c r="G23" s="5"/>
     </row>
@@ -1543,7 +1543,7 @@
         <v>48</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>12</v>
+        <v>161</v>
       </c>
       <c r="G24" s="10"/>
     </row>
@@ -1562,7 +1562,7 @@
         <v>48</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>12</v>
+        <v>161</v>
       </c>
       <c r="G25" s="5"/>
     </row>
@@ -1581,7 +1581,7 @@
         <v>55</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>12</v>
+        <v>161</v>
       </c>
       <c r="G26" s="10"/>
     </row>
@@ -1600,7 +1600,7 @@
         <v>55</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>12</v>
+        <v>161</v>
       </c>
       <c r="G27" s="5"/>
     </row>
@@ -1619,7 +1619,7 @@
         <v>60</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>12</v>
+        <v>161</v>
       </c>
       <c r="G28" s="10"/>
     </row>
@@ -1638,7 +1638,7 @@
         <v>60</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>12</v>
+        <v>161</v>
       </c>
       <c r="G29" s="5"/>
     </row>
@@ -1657,7 +1657,7 @@
         <v>60</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>12</v>
+        <v>161</v>
       </c>
       <c r="G30" s="10"/>
     </row>

--- a/checklist/1783606423.xlsx
+++ b/checklist/1783606423.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="23" documentId="13_ncr:1_{AF79E293-9A8B-438A-B307-67EF33A802E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F9F7A33E-2E57-4B00-BEB9-3E6B98CE199D}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="13_ncr:1_{AF79E293-9A8B-438A-B307-67EF33A802E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3831EF83-AB65-460E-8AA0-392648A1EE5F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -512,6 +512,9 @@
   </si>
   <si>
     <t>Prepare project documentation in Google Doc, Upload in GitHub</t>
+  </si>
+  <si>
+    <t>Done</t>
   </si>
   <si>
     <r>
@@ -588,11 +591,8 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">  InternFirstName_RegdNo_iNeuBytes</t>
+      <t xml:space="preserve">  InternSakshi_INBT021483_iNeuBytes</t>
     </r>
-  </si>
-  <si>
-    <t>Done</t>
   </si>
 </sst>
 </file>
@@ -1155,7 +1155,7 @@
     </row>
     <row r="3" spans="1:7" ht="43.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B3" s="15"/>
       <c r="C3" s="15"/>
@@ -1218,7 +1218,7 @@
         <v>11</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G7" s="5"/>
     </row>
@@ -1237,7 +1237,7 @@
         <v>11</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G8" s="10"/>
     </row>
@@ -1256,7 +1256,7 @@
         <v>11</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G9" s="5"/>
     </row>
@@ -1275,7 +1275,7 @@
         <v>11</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G10" s="10"/>
     </row>
@@ -1294,7 +1294,7 @@
         <v>11</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G11" s="5"/>
     </row>
@@ -1313,7 +1313,7 @@
         <v>11</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G12" s="10"/>
     </row>
@@ -1334,7 +1334,7 @@
         <v>24</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G13" s="5"/>
     </row>
@@ -1353,7 +1353,7 @@
         <v>24</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G14" s="10"/>
     </row>
@@ -1372,7 +1372,7 @@
         <v>29</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G15" s="5"/>
     </row>
@@ -1391,7 +1391,7 @@
         <v>29</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G16" s="10"/>
     </row>
@@ -1410,7 +1410,7 @@
         <v>34</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G17" s="5"/>
     </row>
@@ -1429,7 +1429,7 @@
         <v>34</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G18" s="10"/>
     </row>
@@ -1448,7 +1448,7 @@
         <v>34</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G19" s="5"/>
     </row>
@@ -1467,7 +1467,7 @@
         <v>41</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G20" s="10"/>
     </row>
@@ -1486,7 +1486,7 @@
         <v>41</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G21" s="5"/>
     </row>
@@ -1505,7 +1505,7 @@
         <v>41</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G22" s="10"/>
     </row>
@@ -1524,7 +1524,7 @@
         <v>48</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G23" s="5"/>
     </row>
@@ -1543,7 +1543,7 @@
         <v>48</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G24" s="10"/>
     </row>
@@ -1562,7 +1562,7 @@
         <v>48</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G25" s="5"/>
     </row>
@@ -1581,7 +1581,7 @@
         <v>55</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G26" s="10"/>
     </row>
@@ -1600,7 +1600,7 @@
         <v>55</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G27" s="5"/>
     </row>
@@ -1619,7 +1619,7 @@
         <v>60</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G28" s="10"/>
     </row>
@@ -1638,7 +1638,7 @@
         <v>60</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G29" s="5"/>
     </row>
@@ -1657,7 +1657,7 @@
         <v>60</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G30" s="10"/>
     </row>
